--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -20,7 +20,7 @@
     <t>AT32F415RBT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-004ba7.o</t>
+    <t>lto-llvm-58e035.o</t>
   </si>
   <si>
     <t>startup_at32f415.o</t>
@@ -249,7 +249,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-004ba7.o</c:v>
+                  <c:v>lto-llvm-58e035.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f415.o</c:v>
@@ -344,7 +344,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-004ba7.o</c:v>
+                  <c:v>lto-llvm-58e035.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>mf_w.l</c:v>
@@ -464,112 +464,112 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>95.64986419677734</c:v>
+                  <c:v>95.65325164794922</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.7910236120224</c:v>
+                  <c:v>1.789630055427551</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3574968278408051</c:v>
+                  <c:v>0.3572186529636383</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2955543100833893</c:v>
+                  <c:v>0.2953243255615234</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.205295205116272</c:v>
+                  <c:v>0.2051354646682739</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.201755627989769</c:v>
+                  <c:v>0.2015986442565918</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.1964462697505951</c:v>
+                  <c:v>0.1962934136390686</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1645901203155518</c:v>
+                  <c:v>0.1644620448350906</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1557411849498749</c:v>
+                  <c:v>0.1556200087070465</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1097267419099808</c:v>
+                  <c:v>0.1096413657069206</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.0973382443189621</c:v>
+                  <c:v>0.09726250171661377</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.08848930895328522</c:v>
+                  <c:v>0.08842045813798904</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.05486337095499039</c:v>
+                  <c:v>0.05482068285346031</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.0495540127158165</c:v>
+                  <c:v>0.04951545596122742</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.0477842278778553</c:v>
+                  <c:v>0.04774704575538635</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.04424465447664261</c:v>
+                  <c:v>0.04421022906899452</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.04424465447664261</c:v>
+                  <c:v>0.04421022906899452</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.04247486963868141</c:v>
+                  <c:v>0.04244181886315346</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.03539572283625603</c:v>
+                  <c:v>0.0353681817650795</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.03362593799829483</c:v>
+                  <c:v>0.03359977528452873</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.03185615316033363</c:v>
+                  <c:v>0.03183136507868767</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.03185615316033363</c:v>
+                  <c:v>0.03183136507868767</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.02831657975912094</c:v>
+                  <c:v>0.02829454652965069</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.0265467930585146</c:v>
+                  <c:v>0.02652613632380962</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.0265467930585146</c:v>
+                  <c:v>0.02652613632380962</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.02477700635790825</c:v>
+                  <c:v>0.02475772798061371</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.02477700635790825</c:v>
+                  <c:v>0.02475772798061371</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.02477700635790825</c:v>
+                  <c:v>0.02475772798061371</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.02477700635790825</c:v>
+                  <c:v>0.02475772798061371</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.02477700635790825</c:v>
+                  <c:v>0.02475772798061371</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.02300722151994705</c:v>
+                  <c:v>0.02298931963741779</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.01592807658016682</c:v>
+                  <c:v>0.01591568253934383</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.008848930709064007</c:v>
+                  <c:v>0.008842045441269875</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.007079144939780235</c:v>
+                  <c:v>0.007073636632412672</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.007079144939780235</c:v>
+                  <c:v>0.007073636632412672</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.003539572469890118</c:v>
+                  <c:v>0.003536818316206336</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -1042,10 +1042,10 @@
         <v>11185</v>
       </c>
       <c r="D3" s="1">
-        <v>108092</v>
+        <v>108180</v>
       </c>
       <c r="E3" s="1">
-        <v>32080</v>
+        <v>32168</v>
       </c>
       <c r="F3" s="1">
         <v>75751</v>
@@ -1169,16 +1169,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>95.64986419677734</v>
+        <v>95.65325164794922</v>
       </c>
       <c r="C3" s="1">
-        <v>108092</v>
+        <v>108180</v>
       </c>
       <c r="D3" s="1">
         <v>11185</v>
       </c>
       <c r="E3" s="1">
-        <v>32080</v>
+        <v>32168</v>
       </c>
       <c r="F3" s="1">
         <v>75751</v>
@@ -1195,7 +1195,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>1.7910236120224</v>
+        <v>1.789630055427551</v>
       </c>
       <c r="C4" s="1">
         <v>2024</v>
@@ -1221,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2">
-        <v>0.3574968278408051</v>
+        <v>0.3572186529636383</v>
       </c>
       <c r="C5" s="1">
         <v>404</v>
@@ -1247,7 +1247,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.2955543100833893</v>
+        <v>0.2953243255615234</v>
       </c>
       <c r="C6" s="1">
         <v>334</v>
@@ -1273,7 +1273,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.205295205116272</v>
+        <v>0.2051354646682739</v>
       </c>
       <c r="C7" s="1">
         <v>232</v>
@@ -1299,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.201755627989769</v>
+        <v>0.2015986442565918</v>
       </c>
       <c r="C8" s="1">
         <v>228</v>
@@ -1325,7 +1325,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.1964462697505951</v>
+        <v>0.1962934136390686</v>
       </c>
       <c r="C9" s="1">
         <v>222</v>
@@ -1351,7 +1351,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.1645901203155518</v>
+        <v>0.1644620448350906</v>
       </c>
       <c r="C10" s="1">
         <v>186</v>
@@ -1377,7 +1377,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1557411849498749</v>
+        <v>0.1556200087070465</v>
       </c>
       <c r="C11" s="1">
         <v>176</v>
@@ -1403,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1097267419099808</v>
+        <v>0.1096413657069206</v>
       </c>
       <c r="C12" s="1">
         <v>124</v>
@@ -1429,7 +1429,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.0973382443189621</v>
+        <v>0.09726250171661377</v>
       </c>
       <c r="C13" s="1">
         <v>110</v>
@@ -1455,7 +1455,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.08848930895328522</v>
+        <v>0.08842045813798904</v>
       </c>
       <c r="C14" s="1">
         <v>100</v>
@@ -1481,7 +1481,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.05486337095499039</v>
+        <v>0.05482068285346031</v>
       </c>
       <c r="C15" s="1">
         <v>62</v>
@@ -1507,7 +1507,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.0495540127158165</v>
+        <v>0.04951545596122742</v>
       </c>
       <c r="C16" s="1">
         <v>56</v>
@@ -1533,7 +1533,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.0477842278778553</v>
+        <v>0.04774704575538635</v>
       </c>
       <c r="C17" s="1">
         <v>54</v>
@@ -1559,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.04424465447664261</v>
+        <v>0.04421022906899452</v>
       </c>
       <c r="C18" s="1">
         <v>50</v>
@@ -1585,7 +1585,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.04424465447664261</v>
+        <v>0.04421022906899452</v>
       </c>
       <c r="C19" s="1">
         <v>50</v>
@@ -1611,7 +1611,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.04247486963868141</v>
+        <v>0.04244181886315346</v>
       </c>
       <c r="C20" s="1">
         <v>48</v>
@@ -1637,7 +1637,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.03539572283625603</v>
+        <v>0.0353681817650795</v>
       </c>
       <c r="C21" s="1">
         <v>40</v>
@@ -1663,7 +1663,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.03362593799829483</v>
+        <v>0.03359977528452873</v>
       </c>
       <c r="C22" s="1">
         <v>38</v>
@@ -1689,7 +1689,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.03185615316033363</v>
+        <v>0.03183136507868767</v>
       </c>
       <c r="C23" s="1">
         <v>36</v>
@@ -1715,7 +1715,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.03185615316033363</v>
+        <v>0.03183136507868767</v>
       </c>
       <c r="C24" s="1">
         <v>36</v>
@@ -1741,7 +1741,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.02831657975912094</v>
+        <v>0.02829454652965069</v>
       </c>
       <c r="C25" s="1">
         <v>32</v>
@@ -1767,7 +1767,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.0265467930585146</v>
+        <v>0.02652613632380962</v>
       </c>
       <c r="C26" s="1">
         <v>30</v>
@@ -1793,7 +1793,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.0265467930585146</v>
+        <v>0.02652613632380962</v>
       </c>
       <c r="C27" s="1">
         <v>30</v>
@@ -1819,7 +1819,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.02477700635790825</v>
+        <v>0.02475772798061371</v>
       </c>
       <c r="C28" s="1">
         <v>28</v>
@@ -1845,7 +1845,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.02477700635790825</v>
+        <v>0.02475772798061371</v>
       </c>
       <c r="C29" s="1">
         <v>28</v>
@@ -1871,7 +1871,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.02477700635790825</v>
+        <v>0.02475772798061371</v>
       </c>
       <c r="C30" s="1">
         <v>28</v>
@@ -1897,7 +1897,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.02477700635790825</v>
+        <v>0.02475772798061371</v>
       </c>
       <c r="C31" s="1">
         <v>28</v>
@@ -1923,7 +1923,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.02477700635790825</v>
+        <v>0.02475772798061371</v>
       </c>
       <c r="C32" s="1">
         <v>28</v>
@@ -1949,7 +1949,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.02300722151994705</v>
+        <v>0.02298931963741779</v>
       </c>
       <c r="C33" s="1">
         <v>26</v>
@@ -1975,7 +1975,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.01592807658016682</v>
+        <v>0.01591568253934383</v>
       </c>
       <c r="C34" s="1">
         <v>18</v>
@@ -2001,7 +2001,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.008848930709064007</v>
+        <v>0.008842045441269875</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -2027,7 +2027,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.007079144939780235</v>
+        <v>0.007073636632412672</v>
       </c>
       <c r="C36" s="1">
         <v>8</v>
@@ -2053,7 +2053,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.007079144939780235</v>
+        <v>0.007073636632412672</v>
       </c>
       <c r="C37" s="1">
         <v>8</v>
@@ -2079,7 +2079,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.003539572469890118</v>
+        <v>0.003536818316206336</v>
       </c>
       <c r="C38" s="1">
         <v>4</v>

--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -20,7 +20,7 @@
     <t>AT32F415RBT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-58e035.o</t>
+    <t>lto-llvm-0886c7.o</t>
   </si>
   <si>
     <t>startup_at32f415.o</t>
@@ -249,7 +249,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-58e035.o</c:v>
+                  <c:v>lto-llvm-0886c7.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f415.o</c:v>
@@ -344,7 +344,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-58e035.o</c:v>
+                  <c:v>lto-llvm-0886c7.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>mf_w.l</c:v>
@@ -464,112 +464,112 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>95.65325164794922</c:v>
+                  <c:v>95.65447998046875</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.789630055427551</c:v>
+                  <c:v>1.789123773574829</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3572186529636383</c:v>
+                  <c:v>0.3571175932884216</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2953243255615234</c:v>
+                  <c:v>0.2952407896518707</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2051354646682739</c:v>
+                  <c:v>0.2050774395465851</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2015986442565918</c:v>
+                  <c:v>0.2015416175127029</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.1962934136390686</c:v>
+                  <c:v>0.1962378919124603</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1644620448350906</c:v>
+                  <c:v>0.1644155234098434</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1556200087070465</c:v>
+                  <c:v>0.1555759906768799</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1096413657069206</c:v>
+                  <c:v>0.1096103563904762</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.09726250171661377</c:v>
+                  <c:v>0.09723499417304993</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.08842045813798904</c:v>
+                  <c:v>0.08839544653892517</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.05482068285346031</c:v>
+                  <c:v>0.05480517819523811</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.04951545596122742</c:v>
+                  <c:v>0.0495014488697052</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.04774704575538635</c:v>
+                  <c:v>0.04773354157805443</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.04421022906899452</c:v>
+                  <c:v>0.04419772326946259</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.04421022906899452</c:v>
+                  <c:v>0.04419772326946259</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.04244181886315346</c:v>
+                  <c:v>0.04242981225252152</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.0353681817650795</c:v>
+                  <c:v>0.03535817936062813</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.03359977528452873</c:v>
+                  <c:v>0.03359026834368706</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.03183136507868767</c:v>
+                  <c:v>0.03182236105203629</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.03183136507868767</c:v>
+                  <c:v>0.03182236105203629</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.02829454652965069</c:v>
+                  <c:v>0.02828654274344444</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.02652613632380962</c:v>
+                  <c:v>0.02651863358914852</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.02652613632380962</c:v>
+                  <c:v>0.02651863358914852</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.02475772798061371</c:v>
+                  <c:v>0.0247507244348526</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.02475772798061371</c:v>
+                  <c:v>0.0247507244348526</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.02475772798061371</c:v>
+                  <c:v>0.0247507244348526</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.02475772798061371</c:v>
+                  <c:v>0.0247507244348526</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.02475772798061371</c:v>
+                  <c:v>0.0247507244348526</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.02298931963741779</c:v>
+                  <c:v>0.02298281528055668</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.01591568253934383</c:v>
+                  <c:v>0.01591118052601814</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.008842045441269875</c:v>
+                  <c:v>0.008839544840157032</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.007073636632412672</c:v>
+                  <c:v>0.007071635685861111</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.007073636632412672</c:v>
+                  <c:v>0.007071635685861111</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.003536818316206336</c:v>
+                  <c:v>0.003535817842930555</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -1042,10 +1042,10 @@
         <v>11185</v>
       </c>
       <c r="D3" s="1">
-        <v>108180</v>
+        <v>108212</v>
       </c>
       <c r="E3" s="1">
-        <v>32168</v>
+        <v>32200</v>
       </c>
       <c r="F3" s="1">
         <v>75751</v>
@@ -1169,16 +1169,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>95.65325164794922</v>
+        <v>95.65447998046875</v>
       </c>
       <c r="C3" s="1">
-        <v>108180</v>
+        <v>108212</v>
       </c>
       <c r="D3" s="1">
         <v>11185</v>
       </c>
       <c r="E3" s="1">
-        <v>32168</v>
+        <v>32200</v>
       </c>
       <c r="F3" s="1">
         <v>75751</v>
@@ -1195,7 +1195,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>1.789630055427551</v>
+        <v>1.789123773574829</v>
       </c>
       <c r="C4" s="1">
         <v>2024</v>
@@ -1221,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2">
-        <v>0.3572186529636383</v>
+        <v>0.3571175932884216</v>
       </c>
       <c r="C5" s="1">
         <v>404</v>
@@ -1247,7 +1247,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.2953243255615234</v>
+        <v>0.2952407896518707</v>
       </c>
       <c r="C6" s="1">
         <v>334</v>
@@ -1273,7 +1273,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.2051354646682739</v>
+        <v>0.2050774395465851</v>
       </c>
       <c r="C7" s="1">
         <v>232</v>
@@ -1299,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.2015986442565918</v>
+        <v>0.2015416175127029</v>
       </c>
       <c r="C8" s="1">
         <v>228</v>
@@ -1325,7 +1325,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.1962934136390686</v>
+        <v>0.1962378919124603</v>
       </c>
       <c r="C9" s="1">
         <v>222</v>
@@ -1351,7 +1351,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.1644620448350906</v>
+        <v>0.1644155234098434</v>
       </c>
       <c r="C10" s="1">
         <v>186</v>
@@ -1377,7 +1377,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1556200087070465</v>
+        <v>0.1555759906768799</v>
       </c>
       <c r="C11" s="1">
         <v>176</v>
@@ -1403,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1096413657069206</v>
+        <v>0.1096103563904762</v>
       </c>
       <c r="C12" s="1">
         <v>124</v>
@@ -1429,7 +1429,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.09726250171661377</v>
+        <v>0.09723499417304993</v>
       </c>
       <c r="C13" s="1">
         <v>110</v>
@@ -1455,7 +1455,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.08842045813798904</v>
+        <v>0.08839544653892517</v>
       </c>
       <c r="C14" s="1">
         <v>100</v>
@@ -1481,7 +1481,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.05482068285346031</v>
+        <v>0.05480517819523811</v>
       </c>
       <c r="C15" s="1">
         <v>62</v>
@@ -1507,7 +1507,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.04951545596122742</v>
+        <v>0.0495014488697052</v>
       </c>
       <c r="C16" s="1">
         <v>56</v>
@@ -1533,7 +1533,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.04774704575538635</v>
+        <v>0.04773354157805443</v>
       </c>
       <c r="C17" s="1">
         <v>54</v>
@@ -1559,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.04421022906899452</v>
+        <v>0.04419772326946259</v>
       </c>
       <c r="C18" s="1">
         <v>50</v>
@@ -1585,7 +1585,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.04421022906899452</v>
+        <v>0.04419772326946259</v>
       </c>
       <c r="C19" s="1">
         <v>50</v>
@@ -1611,7 +1611,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.04244181886315346</v>
+        <v>0.04242981225252152</v>
       </c>
       <c r="C20" s="1">
         <v>48</v>
@@ -1637,7 +1637,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.0353681817650795</v>
+        <v>0.03535817936062813</v>
       </c>
       <c r="C21" s="1">
         <v>40</v>
@@ -1663,7 +1663,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.03359977528452873</v>
+        <v>0.03359026834368706</v>
       </c>
       <c r="C22" s="1">
         <v>38</v>
@@ -1689,7 +1689,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.03183136507868767</v>
+        <v>0.03182236105203629</v>
       </c>
       <c r="C23" s="1">
         <v>36</v>
@@ -1715,7 +1715,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.03183136507868767</v>
+        <v>0.03182236105203629</v>
       </c>
       <c r="C24" s="1">
         <v>36</v>
@@ -1741,7 +1741,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.02829454652965069</v>
+        <v>0.02828654274344444</v>
       </c>
       <c r="C25" s="1">
         <v>32</v>
@@ -1767,7 +1767,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.02652613632380962</v>
+        <v>0.02651863358914852</v>
       </c>
       <c r="C26" s="1">
         <v>30</v>
@@ -1793,7 +1793,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.02652613632380962</v>
+        <v>0.02651863358914852</v>
       </c>
       <c r="C27" s="1">
         <v>30</v>
@@ -1819,7 +1819,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.02475772798061371</v>
+        <v>0.0247507244348526</v>
       </c>
       <c r="C28" s="1">
         <v>28</v>
@@ -1845,7 +1845,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.02475772798061371</v>
+        <v>0.0247507244348526</v>
       </c>
       <c r="C29" s="1">
         <v>28</v>
@@ -1871,7 +1871,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.02475772798061371</v>
+        <v>0.0247507244348526</v>
       </c>
       <c r="C30" s="1">
         <v>28</v>
@@ -1897,7 +1897,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.02475772798061371</v>
+        <v>0.0247507244348526</v>
       </c>
       <c r="C31" s="1">
         <v>28</v>
@@ -1923,7 +1923,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.02475772798061371</v>
+        <v>0.0247507244348526</v>
       </c>
       <c r="C32" s="1">
         <v>28</v>
@@ -1949,7 +1949,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.02298931963741779</v>
+        <v>0.02298281528055668</v>
       </c>
       <c r="C33" s="1">
         <v>26</v>
@@ -1975,7 +1975,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.01591568253934383</v>
+        <v>0.01591118052601814</v>
       </c>
       <c r="C34" s="1">
         <v>18</v>
@@ -2001,7 +2001,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.008842045441269875</v>
+        <v>0.008839544840157032</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -2027,7 +2027,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.007073636632412672</v>
+        <v>0.007071635685861111</v>
       </c>
       <c r="C36" s="1">
         <v>8</v>
@@ -2053,7 +2053,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.007073636632412672</v>
+        <v>0.007071635685861111</v>
       </c>
       <c r="C37" s="1">
         <v>8</v>
@@ -2079,7 +2079,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.003536818316206336</v>
+        <v>0.003535817842930555</v>
       </c>
       <c r="C38" s="1">
         <v>4</v>

--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -20,7 +20,7 @@
     <t>AT32F415RBT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-0886c7.o</t>
+    <t>lto-llvm-d04348.o</t>
   </si>
   <si>
     <t>startup_at32f415.o</t>
@@ -249,7 +249,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-0886c7.o</c:v>
+                  <c:v>lto-llvm-d04348.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f415.o</c:v>
@@ -344,7 +344,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-0886c7.o</c:v>
+                  <c:v>lto-llvm-d04348.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>mf_w.l</c:v>
@@ -464,112 +464,112 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>95.65447998046875</c:v>
+                  <c:v>95.65593719482422</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.789123773574829</c:v>
+                  <c:v>1.788523077964783</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3571175932884216</c:v>
+                  <c:v>0.3569976985454559</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2952407896518707</c:v>
+                  <c:v>0.2951416373252869</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2050774395465851</c:v>
+                  <c:v>0.2050085663795471</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2015416175127029</c:v>
+                  <c:v>0.2014739364385605</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.1962378919124603</c:v>
+                  <c:v>0.1961719989776611</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1644155234098434</c:v>
+                  <c:v>0.1643603146076202</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1555759906768799</c:v>
+                  <c:v>0.1555237472057343</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1096103563904762</c:v>
+                  <c:v>0.1095735505223274</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.09723499417304993</c:v>
+                  <c:v>0.09720233827829361</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.08839544653892517</c:v>
+                  <c:v>0.08836576342582703</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.05480517819523811</c:v>
+                  <c:v>0.05478677526116371</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.0495014488697052</c:v>
+                  <c:v>0.04948482662439346</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.04773354157805443</c:v>
+                  <c:v>0.04771751165390015</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.04419772326946259</c:v>
+                  <c:v>0.04418288171291351</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.04419772326946259</c:v>
+                  <c:v>0.04418288171291351</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.04242981225252152</c:v>
+                  <c:v>0.0424155667424202</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.03535817936062813</c:v>
+                  <c:v>0.03534630686044693</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.03359026834368706</c:v>
+                  <c:v>0.03357899188995361</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.03182236105203629</c:v>
+                  <c:v>0.03181167319417</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.03182236105203629</c:v>
+                  <c:v>0.03181167319417</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.02828654274344444</c:v>
+                  <c:v>0.02827704511582851</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.02651863358914852</c:v>
+                  <c:v>0.02650972828269005</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.02651863358914852</c:v>
+                  <c:v>0.02650972828269005</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.0247507244348526</c:v>
+                  <c:v>0.02474241331219673</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.0247507244348526</c:v>
+                  <c:v>0.02474241331219673</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.0247507244348526</c:v>
+                  <c:v>0.02474241331219673</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.0247507244348526</c:v>
+                  <c:v>0.02474241331219673</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.0247507244348526</c:v>
+                  <c:v>0.02474241331219673</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.02298281528055668</c:v>
+                  <c:v>0.02297509834170342</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.01591118052601814</c:v>
+                  <c:v>0.015905836597085</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.008839544840157032</c:v>
+                  <c:v>0.008836576715111733</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.007071635685861111</c:v>
+                  <c:v>0.007069261278957129</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.007071635685861111</c:v>
+                  <c:v>0.007069261278957129</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.003535817842930555</c:v>
+                  <c:v>0.003534630639478564</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -1042,10 +1042,10 @@
         <v>11185</v>
       </c>
       <c r="D3" s="1">
-        <v>108212</v>
+        <v>108250</v>
       </c>
       <c r="E3" s="1">
-        <v>32200</v>
+        <v>32238</v>
       </c>
       <c r="F3" s="1">
         <v>75751</v>
@@ -1169,16 +1169,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>95.65447998046875</v>
+        <v>95.65593719482422</v>
       </c>
       <c r="C3" s="1">
-        <v>108212</v>
+        <v>108250</v>
       </c>
       <c r="D3" s="1">
         <v>11185</v>
       </c>
       <c r="E3" s="1">
-        <v>32200</v>
+        <v>32238</v>
       </c>
       <c r="F3" s="1">
         <v>75751</v>
@@ -1195,7 +1195,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>1.789123773574829</v>
+        <v>1.788523077964783</v>
       </c>
       <c r="C4" s="1">
         <v>2024</v>
@@ -1221,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2">
-        <v>0.3571175932884216</v>
+        <v>0.3569976985454559</v>
       </c>
       <c r="C5" s="1">
         <v>404</v>
@@ -1247,7 +1247,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.2952407896518707</v>
+        <v>0.2951416373252869</v>
       </c>
       <c r="C6" s="1">
         <v>334</v>
@@ -1273,7 +1273,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.2050774395465851</v>
+        <v>0.2050085663795471</v>
       </c>
       <c r="C7" s="1">
         <v>232</v>
@@ -1299,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.2015416175127029</v>
+        <v>0.2014739364385605</v>
       </c>
       <c r="C8" s="1">
         <v>228</v>
@@ -1325,7 +1325,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.1962378919124603</v>
+        <v>0.1961719989776611</v>
       </c>
       <c r="C9" s="1">
         <v>222</v>
@@ -1351,7 +1351,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.1644155234098434</v>
+        <v>0.1643603146076202</v>
       </c>
       <c r="C10" s="1">
         <v>186</v>
@@ -1377,7 +1377,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1555759906768799</v>
+        <v>0.1555237472057343</v>
       </c>
       <c r="C11" s="1">
         <v>176</v>
@@ -1403,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1096103563904762</v>
+        <v>0.1095735505223274</v>
       </c>
       <c r="C12" s="1">
         <v>124</v>
@@ -1429,7 +1429,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.09723499417304993</v>
+        <v>0.09720233827829361</v>
       </c>
       <c r="C13" s="1">
         <v>110</v>
@@ -1455,7 +1455,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.08839544653892517</v>
+        <v>0.08836576342582703</v>
       </c>
       <c r="C14" s="1">
         <v>100</v>
@@ -1481,7 +1481,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.05480517819523811</v>
+        <v>0.05478677526116371</v>
       </c>
       <c r="C15" s="1">
         <v>62</v>
@@ -1507,7 +1507,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.0495014488697052</v>
+        <v>0.04948482662439346</v>
       </c>
       <c r="C16" s="1">
         <v>56</v>
@@ -1533,7 +1533,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.04773354157805443</v>
+        <v>0.04771751165390015</v>
       </c>
       <c r="C17" s="1">
         <v>54</v>
@@ -1559,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.04419772326946259</v>
+        <v>0.04418288171291351</v>
       </c>
       <c r="C18" s="1">
         <v>50</v>
@@ -1585,7 +1585,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.04419772326946259</v>
+        <v>0.04418288171291351</v>
       </c>
       <c r="C19" s="1">
         <v>50</v>
@@ -1611,7 +1611,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.04242981225252152</v>
+        <v>0.0424155667424202</v>
       </c>
       <c r="C20" s="1">
         <v>48</v>
@@ -1637,7 +1637,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.03535817936062813</v>
+        <v>0.03534630686044693</v>
       </c>
       <c r="C21" s="1">
         <v>40</v>
@@ -1663,7 +1663,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.03359026834368706</v>
+        <v>0.03357899188995361</v>
       </c>
       <c r="C22" s="1">
         <v>38</v>
@@ -1689,7 +1689,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.03182236105203629</v>
+        <v>0.03181167319417</v>
       </c>
       <c r="C23" s="1">
         <v>36</v>
@@ -1715,7 +1715,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.03182236105203629</v>
+        <v>0.03181167319417</v>
       </c>
       <c r="C24" s="1">
         <v>36</v>
@@ -1741,7 +1741,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.02828654274344444</v>
+        <v>0.02827704511582851</v>
       </c>
       <c r="C25" s="1">
         <v>32</v>
@@ -1767,7 +1767,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.02651863358914852</v>
+        <v>0.02650972828269005</v>
       </c>
       <c r="C26" s="1">
         <v>30</v>
@@ -1793,7 +1793,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.02651863358914852</v>
+        <v>0.02650972828269005</v>
       </c>
       <c r="C27" s="1">
         <v>30</v>
@@ -1819,7 +1819,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.0247507244348526</v>
+        <v>0.02474241331219673</v>
       </c>
       <c r="C28" s="1">
         <v>28</v>
@@ -1845,7 +1845,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.0247507244348526</v>
+        <v>0.02474241331219673</v>
       </c>
       <c r="C29" s="1">
         <v>28</v>
@@ -1871,7 +1871,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.0247507244348526</v>
+        <v>0.02474241331219673</v>
       </c>
       <c r="C30" s="1">
         <v>28</v>
@@ -1897,7 +1897,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.0247507244348526</v>
+        <v>0.02474241331219673</v>
       </c>
       <c r="C31" s="1">
         <v>28</v>
@@ -1923,7 +1923,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.0247507244348526</v>
+        <v>0.02474241331219673</v>
       </c>
       <c r="C32" s="1">
         <v>28</v>
@@ -1949,7 +1949,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.02298281528055668</v>
+        <v>0.02297509834170342</v>
       </c>
       <c r="C33" s="1">
         <v>26</v>
@@ -1975,7 +1975,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.01591118052601814</v>
+        <v>0.015905836597085</v>
       </c>
       <c r="C34" s="1">
         <v>18</v>
@@ -2001,7 +2001,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.008839544840157032</v>
+        <v>0.008836576715111733</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -2027,7 +2027,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.007071635685861111</v>
+        <v>0.007069261278957129</v>
       </c>
       <c r="C36" s="1">
         <v>8</v>
@@ -2053,7 +2053,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.007071635685861111</v>
+        <v>0.007069261278957129</v>
       </c>
       <c r="C37" s="1">
         <v>8</v>
@@ -2079,7 +2079,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.003535817842930555</v>
+        <v>0.003534630639478564</v>
       </c>
       <c r="C38" s="1">
         <v>4</v>

--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -20,7 +20,7 @@
     <t>AT32F415RBT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-d04348.o</t>
+    <t>lto-llvm-13053d.o</t>
   </si>
   <si>
     <t>startup_at32f415.o</t>
@@ -249,7 +249,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-d04348.o</c:v>
+                  <c:v>lto-llvm-13053d.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f415.o</c:v>
@@ -344,7 +344,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-d04348.o</c:v>
+                  <c:v>lto-llvm-13053d.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>mf_w.l</c:v>

--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -20,7 +20,7 @@
     <t>AT32F415RBT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-13053d.o</t>
+    <t>lto-llvm-c5f3d7.o</t>
   </si>
   <si>
     <t>startup_at32f415.o</t>
@@ -249,7 +249,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-13053d.o</c:v>
+                  <c:v>lto-llvm-c5f3d7.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f415.o</c:v>
@@ -344,7 +344,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-13053d.o</c:v>
+                  <c:v>lto-llvm-c5f3d7.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>mf_w.l</c:v>
